--- a/CoreEngine/GameData/Test/TestRefereceTable.xlsx
+++ b/CoreEngine/GameData/Test/TestRefereceTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\CoreFramework Develop\Assets\_WorkSpace\CoreFramework\CoreEngine\GameData\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17F74D9-B2EF-4603-88DF-CFFFA8D93203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DAEDEF-7A49-4AA2-B700-A04E8D1C5FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>{spriteIdTest}</t>
   </si>
@@ -38,85 +38,115 @@
     <t>{recordIdArrayTest}</t>
   </si>
   <si>
+    <t>Ref_01</t>
+  </si>
+  <si>
+    <t>&lt;1&gt;_&lt;10.5&gt;_&lt;True&gt;_&lt;Alpha&gt;</t>
+  </si>
+  <si>
+    <t>1001|1002</t>
+  </si>
+  <si>
+    <t>Ref_02</t>
+  </si>
+  <si>
+    <t>&lt;2&gt;_&lt;10.5&gt;_&lt;True&gt;_&lt;Bravo&gt;</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>Ref_03</t>
+  </si>
+  <si>
+    <t>&lt;3&gt;_&lt;12&gt;_&lt;False&gt;_&lt;Charlie&gt;</t>
+  </si>
+  <si>
+    <t>1001|1004|1005</t>
+  </si>
+  <si>
+    <t>&lt;4&gt;_&lt;12&gt;_&lt;False&gt;_&lt;Delta&gt;</t>
+  </si>
+  <si>
+    <t>Ref_04</t>
+  </si>
+  <si>
+    <t>1002|1005</t>
+  </si>
+  <si>
+    <t>&lt;5&gt;_&lt;15.25&gt;_&lt;True&gt;_&lt;Echo&gt;|&lt;1&gt;_&lt;10.5&gt;_&lt;True&gt;_&lt;Alpha&gt;</t>
+  </si>
+  <si>
+    <t>Ref_05</t>
+  </si>
+  <si>
+    <t>&lt;5&gt;_&lt;15.25&gt;_&lt;True&gt;_&lt;Echo&gt;</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>&lt;3&gt;_&lt;12&gt;_&lt;False&gt;_&lt;Charlie&gt;|&lt;4&gt;_&lt;12&gt;_&lt;False&gt;_&lt;Delta&gt;</t>
+  </si>
+  <si>
+    <t>TestReferenceRecord Test Data</t>
+  </si>
+  <si>
+    <t>ForeignKey format</t>
+  </si>
+  <si>
+    <t>ForeignKey&lt;TestRecord, TestTable&gt; stores the original string key.</t>
+  </si>
+  <si>
+    <t>TestTable key rule</t>
+  </si>
+  <si>
+    <t>intTest/floatTest/boolTest/stringTest, separated by '/'</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
     <t>1/10.5/True/Alpha</t>
   </si>
   <si>
-    <t>101|102|103</t>
+    <t>Hash</t>
+  </si>
+  <si>
+    <t>ForeignKey(string key) internally calculates HashHelper.StringToId(key).</t>
+  </si>
+  <si>
+    <t>ForeignKey array</t>
+  </si>
+  <si>
+    <t>Each ForeignKey element is a TestTable string key; elements are separated by '|'.</t>
+  </si>
+  <si>
+    <t>Example array</t>
   </si>
   <si>
     <t>1/10.5/True/Alpha|2/10.5/True/Bravo|3/12/False/Charlie</t>
   </si>
   <si>
-    <t>4/12/False/Delta</t>
-  </si>
-  <si>
-    <t>104|105</t>
-  </si>
-  <si>
-    <t>4/12/False/Delta|5/15.25/True/Echo</t>
-  </si>
-  <si>
-    <t>6/15.25/False/Foxtrot</t>
-  </si>
-  <si>
-    <t>6/15.25/False/Foxtrot|7/18.75/True/Golf|8/18.75/False/Hotel</t>
-  </si>
-  <si>
-    <t>9/20/True/India</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>10/20/False/Juliet</t>
-  </si>
-  <si>
-    <t>110|111</t>
-  </si>
-  <si>
-    <t>10/20/False/Juliet|11/22.5/True/Kilo</t>
-  </si>
-  <si>
-    <t>TestReferenceRecord Test Data</t>
-  </si>
-  <si>
-    <t>ForeignKey format</t>
-  </si>
-  <si>
-    <t>ForeignKey&lt;TestRecord, TestTable&gt; stores the original string key.</t>
-  </si>
-  <si>
-    <t>TestTable key rule</t>
-  </si>
-  <si>
-    <t>intTest/floatTest/boolTest/stringTest, separated by '/'</t>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>Hash</t>
-  </si>
-  <si>
-    <t>ForeignKey(string key) internally calculates HashHelper.StringToId(key).</t>
-  </si>
-  <si>
-    <t>ForeignKey array</t>
-  </si>
-  <si>
-    <t>Each ForeignKey element is a TestTable string key; elements are separated by '|'.</t>
-  </si>
-  <si>
-    <t>Example array</t>
-  </si>
-  <si>
     <t>Referenced TestTable rows</t>
   </si>
   <si>
     <t>The five single FK values and all array FK values reference rows from the previously generated TestTable data.</t>
   </si>
   <si>
-    <t>106|107|108</t>
+    <t>&lt;2&gt;_&lt;10.5&gt;_&lt;True&gt;_&lt;Bravo&gt;|&lt;3&gt;_&lt;12&gt;_&lt;False&gt;_&lt;Charlie&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;1&gt;_&lt;10.5&gt;_&lt;True&gt;_&lt;Alpha&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{tempPK}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;4&gt;_&lt;12&gt;_&lt;False&gt;_&lt;DeltaTrash&gt;</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -505,35 +535,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="75" customWidth="1"/>
+    <col min="1" max="1" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.25" customWidth="1"/>
+    <col min="4" max="4" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="72.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>101</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1001</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -541,13 +575,16 @@
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>102</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>7</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1002</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
@@ -555,47 +592,59 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>103</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B4" s="2">
+        <v>1003</v>
+      </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>104</v>
-      </c>
-      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1004</v>
+      </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>105</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1005</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -614,65 +663,65 @@
     <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
